--- a/docs/submission/figures_for_review/Table_S2.xlsx
+++ b/docs/submission/figures_for_review/Table_S2.xlsx
@@ -17,9 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -70,18 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -449,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -630,12 +622,14 @@
           <t>detection_power (35 types, signal=3.0)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Detection rate at near-calibrated signal with 35 types</t>
+          <t>Detection rate under the planted signal. Signal strength = 3.0 used as the nearest simulated setpoint to the calibrated strength (3.68); the 0.68 gap has negligible effect on detection power at n=35 (&gt;99% under either setpoint).</t>
         </is>
       </c>
     </row>
@@ -645,8 +639,10 @@
           <t>false_positive_rate (alpha=0.05)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>0.048</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -660,8 +656,10 @@
           <t>false_positive_rate (alpha=0.01)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0.008999999999999999</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -672,90 +670,152 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ranking_recovery_ceiling (rho)</t>
+          <t>ranking_recovery_ceiling (rho, calibrated signal)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.418</v>
+        <v>0.449</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Spearman rho between planted and recovered rankings at calibrated signal</t>
+          <t>Median Spearman rho between planted and recovered rankings at the calibrated signal (3.68), 200 cells/type, 100 replicates. Read from the deposited spread sweep (sigma = 1.0), which is the artifact Fig 4C plots; the recovery grid below does not evaluate at the calibrated signal.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ranking_recovery_ceiling_sub_calibration (rho, signal=2.0)</t>
+          <t>recovery median rho (signal 3.0, 200 cells/type)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.231</v>
+        <v>0.422</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Sub-calibration sensitivity: Spearman rho at signal=2.0, n_cells=200, n_types=35, 100 reps (std 0.197)</t>
+          <t>Median Spearman rho at the nearer bracketing signal the deposited grid does evaluate, and the value Fig 4C plots for this curve at 200 cells/type; 100 replicates (std 0.173).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ranking_recovery_ceiling_super_calibration (rho, signal=7.0)</t>
+          <t>recovery mean rho (signal 2.0, 200 cells/type)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.367</v>
+        <v>0.231</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Super-calibration sensitivity: Spearman rho at signal=7.0, n_cells=200, n_types=35, 100 reps (std 0.149)</t>
+          <t>Sub-calibration sensitivity: mean Spearman rho at signal = 2.0, n_cells = 200, n_types = 35, 100 reps (std 0.197). Not a ceiling.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>test_retest_rho (200 cells/type)</t>
+          <t>recovery mean rho (signal 7.0, 200 cells/type)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.994</v>
+        <v>0.367</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Within-atlas test-retest Spearman rho at calibrated signal, 200 cells/type</t>
+          <t>Super-calibration sensitivity: mean Spearman rho at signal = 7.0, n_cells = 200, n_types = 35, 100 reps (std 0.149). Not a ceiling.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>null_p_value_mean</t>
+          <t>test_retest_rho (200 cells/type)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.507</v>
+        <v>0.994</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mean p-value under null (expected: 0.5)</t>
+          <t>Within-atlas test-retest Spearman rho at calibrated signal, 200 cells/type</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>null_p_value_mean</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mean p-value under null (expected: 0.5). Diagnostic check: null distribution p-value mean should approximate 0.5 for a well-calibrated permutation test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>null_replicates</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Number of null-hypothesis replicates for calibration check</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>bootstrap_n_iterations</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bootstrap iterations for per-type ranking CIs (Sheet 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bootstrap_resampling_scheme</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cells resampled with replacement within type (full n per type, no subsampling)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Resampling unit for the Sheet 2 ranking-stability bootstrap, per S1 Text section 11: PCA and Procrustes are refit per iteration. Distinct from the global robustness bootstrap, which uses 100 iterations at 50% cell subsampling per type per species.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bootstrap_random_seed</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>42</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Global seed for bootstrap resampling and permutation tests</t>
         </is>
       </c>
     </row>
